--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_948_Morocco_South.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_948_Morocco_South.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rdebfd95f509f434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7276b20d0e38487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R78c96117ed0c4e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R68c50bd07da24d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd468ccd9f03f4fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R34942140607a48ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R871fd8af8b7e4d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7ce3b4b8ee7c4800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R22ffb3146d5c4895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R74ea8efe76644655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfa86fb456d714d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8cce3bfcfd594a73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ948CommercialTable" displayName="EEZ948CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ948CommercialTable" displayName="EEZ948CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ948FunctionalTable" displayName="EEZ948FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ948FunctionalTable" displayName="EEZ948FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ948ValidationTable" displayName="EEZ948ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ948ValidationTable" displayName="EEZ948ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -15903,7 +15857,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e6732d90544472b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5330290326aa432d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15913,20 +15867,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -15934,714 +15878,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12772.5066828009</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12772.5066828009</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$228,A2,'Species'!$U$2:$U$228))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1645417.6008115814</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1645417.6008115814</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8502.79321682</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.396879634399881</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2493.903440734149</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8502.79321682</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2596.0329659102654</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$228,A3,'Species'!$U$2:$U$228))</x:f>
-        <x:v>22073531.493182912</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.396879634399881</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2493.903440734149</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>21205145.259278383</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>868386.2339045294</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0409516757978616</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.04095167579786156</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>18748.726305024404</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.0850512639504726</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>121.63295672384469</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>18748.726305024404</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>129.1715663520321</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$228,A4,'Species'!$U$2:$U$228))</x:f>
-        <x:v>2421802.3439255496</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.0850512639504726</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>121.63295672384469</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2280463.0152862417</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>141339.328639308</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.06197834724435</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.06197834724434994</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5982.8096511044005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4099093599006665</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>256.9859380331916</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5982.8096511044005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>278.97752855987505</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$228,A5,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1669069.450309274</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4099093599006665</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>256.9859380331916</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1537497.950263096</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>131571.500046178</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0855750734650824</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08557507346508236</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>683481.1358511486</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0620666787636184</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>115.36303651637512</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>683481.1358511486</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>115.595296012336</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$228,A6,'Species'!$U$2:$U$228))</x:f>
-        <x:v>79007204.21756116</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0620666787636184</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>115.36303651637512</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>78848459.23344961</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>158744.98411154747</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0020132921512332</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0020132921512333577</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>871.813788042</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.25930727480112</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>18.16800642516443</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>871.813788042</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>20.711651014054013</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$228,A7,'Species'!$U$2:$U$228))</x:f>
-        <x:v>18056.70292716636</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.25930727480112</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>18.16800642516443</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>15839.118502693998</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2217.584424472361</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.140006808086901</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.140006808086901</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>694306.2906507633</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.329151251109624</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>213.37879149808202</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>694306.2906507633</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>251.30638142938702</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$228,A8,'Species'!$U$2:$U$228))</x:f>
-        <x:v>174483601.50710356</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.329151251109624</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>213.37879149808202</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>148150237.22857597</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>26333364.278527588</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1777477024076495</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.17774770240764942</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>241118.85331860505</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.82026111820238</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>661.0908073256061</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>241118.85331860505</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>773.5206555719117</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$228,A9,'Species'!$U$2:$U$228))</x:f>
-        <x:v>186510413.48975497</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.82026111820238</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>661.0908073256061</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>159401457.40182102</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>27108956.087933958</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1700671783671175</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.17006717836711738</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>164.9003004687</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>164.9003004687</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>416.86938347033555</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$228,A10,'Species'!$U$2:$U$228))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>68741.88659046005</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>68741.88659046005</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>7418.036593609199</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.712116659137805</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>515.3670626493561</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>7418.036593609199</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>557.0976890957782</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$228,A11,'Species'!$U$2:$U$228))</x:f>
-        <x:v>4132571.043927603</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.712116659137805</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>515.3670626493561</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3823011.729873808</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>309559.31405379483</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0809726299385467</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.08097262993854662</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>17247.796494528102</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.075134175692861</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1188.8694730570498</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>17247.796494528102</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1489.734590173285</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$228,A12,'Species'!$U$2:$U$228))</x:f>
-        <x:v>25694639.042168044</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.075134175692861</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1188.8694730570498</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>20505378.729844857</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>5189260.312323187</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2530682500767665</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2530682500767665</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>18083.646630491698</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.397451759765336</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2497.190992651959</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>18083.646630491698</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2592.511393448063</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$228,A13,'Species'!$U$2:$U$228))</x:f>
-        <x:v>46882059.9246384</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.397451759765336</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2497.190992651959</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>45158319.479964815</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1723740.444673583</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0381710494217649</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.038171049421764844</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd942d88140dd4072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ce9461135d461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16651,20 +16131,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16672,1362 +16142,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>75064.09610768918</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.70113333406572</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>502.4968389210331</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>75064.09610768918</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>575.1917865517494</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$228,A2,'Species'!$U$2:$U$228))</x:f>
-        <x:v>43176251.54607396</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.70113333406572</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>502.4968389210331</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>37719471.01057844</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5456780.53549552</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1446674725094943</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1446674725094942</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1889.2742904419</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8340516604040102</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>682.4198648465582</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1889.2742904419</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>705.0181179001157</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$228,A3,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1331972.6044444249</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8340516604040102</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>682.4198648465582</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1289278.3059414385</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>42694.29850298632</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0331148816405553</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.03311488164055525</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>24.9209499898</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>24.9209499898</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$228,A4,'Species'!$U$2:$U$228))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>54521.09802005042</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>54521.09802005042</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6727.060797827299</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.376814964615435</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2381.30467519378</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6727.060797827299</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2477.4284735373435</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$228,A5,'Species'!$U$2:$U$228))</x:f>
-        <x:v>16665811.96375419</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.376814964615435</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2381.30467519378</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>16019181.328178948</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>646630.6355752423</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.040366022603026</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04036602260302593</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8514.1166251671</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.339433950784991</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2184.912004362454</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8514.1166251671</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2239.6379835020957</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$228,A6,'Species'!$U$2:$U$228))</x:f>
-        <x:v>19068538.98969091</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.339433950784991</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2184.912004362454</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>18602595.62086954</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>465943.36882137135</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0250472234261034</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.02504722342610336</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>16115.9449627979</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.357083418773253</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2275.534470782252</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>16115.9449627979</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2337.8169082670465</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$228,A7,'Species'!$U$2:$U$228))</x:f>
-        <x:v>37676128.62673007</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.357083418773253</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2275.534470782252</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>36672388.292076215</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1003740.3346538544</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0273704653937341</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.027370465393734174</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3001.0848248707</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.517082317399567</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>328.91396824813324</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3001.0848248707</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>342.3760412675801</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$228,A8,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1027499.5418474391</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.517082317399567</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>328.91396824813324</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>987098.7187974759</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>40400.82304996322</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0409288577531346</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.04092885775313451</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2304.3273123156996</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.926218295012916</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>843.7587604962363</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2304.3273123156996</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>865.5542407706772</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$228,A9,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1994520.2772985506</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.926218295012916</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>843.7587604962363</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1944296.3568171181</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>50223.92048143246</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0258314121226102</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.025831412122610153</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12368.773405459599</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.249335887473513</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1775.5621866341394</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12368.773405459599</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1894.0879997816269</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$228,A10,'Species'!$U$2:$U$228))</x:f>
-        <x:v>23427545.27929915</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.249335887473513</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1775.5621866341394</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>21961526.353780035</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1466018.9255191162</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.066753963358598</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.06675396335859797</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3286.6424588003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1376256338550608</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>137.28580475725383</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3286.6424588003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>137.50492925352896</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$228,A11,'Species'!$U$2:$U$228))</x:f>
-        <x:v>451929.5387789797</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1376256338550608</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>137.28580475725383</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>451209.35490575864</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>720.1838732210454</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0015961191083271</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0015961191083271441</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4085.7456608680995</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.8562539002666205</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>718.2140558631477</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4085.7456608680995</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1136.513390158371</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$228,A12,'Species'!$U$2:$U$228))</x:f>
-        <x:v>4643504.652358058</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.8562539002666205</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>718.2140558631477</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2934439.9623173345</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1709064.6900407234</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.5824159676080307</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.5824159676080307</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>6046.7940338966</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>6046.7940338966</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$228,A13,'Species'!$U$2:$U$228))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7269845.410410643</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>7269845.410410643</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>10925.954989583</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.60116744075105</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>399.17877470808844</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>10925.954989583</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>801.5998889787514</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$228,A14,'Species'!$U$2:$U$228))</x:f>
-        <x:v>8758244.306636568</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.60116744075105</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>399.17877470808844</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4361409.325257467</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>4396834.981379101</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.0081225249637726</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.0081225249637724</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>617907.9073018412</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2905896427610255</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>195.24937068454946</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>617907.9073018412</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>209.05737782563332</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$228,A15,'Species'!$U$2:$U$228))</x:f>
-        <x:v>129178206.83824743</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2905896427610255</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>195.24937068454946</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>120646130.04169142</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8532076.79655601</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0707198547819776</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.07071985478197768</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>207940.387428647</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.836427790322069</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>686.1637812100105</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>207940.387428647</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>773.1394421337666</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$228,A16,'Species'!$U$2:$U$228))</x:f>
-        <x:v>160766915.13366342</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.836427790322069</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>686.1637812100105</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>142681162.50431496</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>18085752.629348457</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1267564148757303</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.12675641487573042</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>4165.764108137401</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.605321515337729</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>403.01528274560394</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>4165.764108137401</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>647.3212237528054</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$228,A17,'Species'!$U$2:$U$228))</x:f>
-        <x:v>2696587.5203450164</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.605321515337729</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>403.01528274560394</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1678866.5998924833</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1017720.920452533</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.6061952274931846</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.6061952274931844</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>18134.510446572804</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.749750885285674</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>56.20188542991626</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>18134.510446572804</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>68.66731108452343</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$228,A18,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1245248.0702003548</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.749750885285674</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>56.20188542991626</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1019193.6784459043</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>226054.3917544505</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2217972859674175</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.22179728596741763</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>5028.157458749</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2271759839320273</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>168.72365854823758</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>5028.157458749</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>184.2583837121057</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$228,A19,'Species'!$U$2:$U$228))</x:f>
-        <x:v>926480.1663990597</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2271759839320273</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>168.72365854823758</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>848369.1221967404</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>78111.04420231935</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.092072002809415</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.09207200280941516</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>3730.3415226917996</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.47083612571858</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>295.68965170193303</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>3730.3415226917996</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>297.1272105727647</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$228,A20,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1108385.971121174</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.47083612571858</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>295.68965170193303</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1103023.3855739967</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>5362.585547177354</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0048617151887371</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.004861715188737132</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>693571.9446891766</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0624166839814024</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>115.45604699957077</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>693571.9446891766</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>115.67325323658814</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$228,A21,'Species'!$U$2:$U$228))</x:f>
-        <x:v>80227723.19582403</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0624166839814024</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>115.45604699957077</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>80077075.04361728</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>150648.15220674872</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0018812893968054</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0018812893968054153</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>4.812192581200001</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.7299999999999995</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>537.0317963702522</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>4.812192581200001</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$228,A22,'Species'!$U$2:$U$228))</x:f>
-        <x:v>2584.3004263614393</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.7299999999999995</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>537.0317963702522</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>2584.300426361437</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>2.2737367544323206e-12</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>8.798267922873138e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>5982.8096511044005</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.4099093599006665</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>256.9859380331916</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>5982.8096511044005</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>278.97752855987505</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$228,A23,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1669069.450309274</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.4099093599006665</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>256.9859380331916</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1537497.950263096</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>131571.500046178</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0855750734650824</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.08557507346508236</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>39.1913230392</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.7998870056492966</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>630.7932039153206</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>39.1913230392</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>630.8388022656414</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$228,A24,'Species'!$U$2:$U$228))</x:f>
-        <x:v>24723.40728525477</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.7998870056492966</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>630.7932039153206</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>24721.62022557729</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>1.787059677477373</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0000722873202148</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.00007228732021489672</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1838.7469411585998</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.820007586391381</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>660.7049893074898</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1838.7469411585998</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>660.7058244625551</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$228,A25,'Species'!$U$2:$U$228))</x:f>
-        <x:v>1214870.813736194</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.820007586391381</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>660.7049893074898</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>1214869.2780973723</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>1.5356388217769563</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0000012640362625</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.000001264036262553241</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1b01de025714de1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0ef14c9040141f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18202,7 +16788,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -18301,7 +16887,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>544607108.7029005</x:v>
+        <x:v>482639968.63426256</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18315,7 +16901,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>544607108.7029006</x:v>
+        <x:v>501100754.66269565</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18329,7 +16915,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-61967140.06863809</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18343,7 +16929,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-43506354.040205</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18354,9 +16940,9 @@
         <x:v>EEZ_948</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -18368,47 +16954,19 @@
         <x:v>EEZ_948</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_948</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_948</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b49a37ccb3b4b56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f88619cdab4406"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18455,7 +17013,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
